--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0003T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.2940284802584</v>
+        <v>3.46027962804199</v>
       </c>
       <c r="D2" t="n">
-        <v>21.87043034652503</v>
+        <v>3.553944931310317</v>
       </c>
       <c r="E2" t="n">
-        <v>6.451612669012473</v>
+        <v>1.048387058714527</v>
       </c>
       <c r="F2" t="n">
-        <v>6.269949629657978</v>
+        <v>1.018866814819422</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.59315583741011</v>
+        <v>5.296387823579143</v>
       </c>
       <c r="D3" t="n">
-        <v>32.20254061804</v>
+        <v>5.2329128504315</v>
       </c>
       <c r="E3" t="n">
-        <v>6.451612669012473</v>
+        <v>1.048387058714527</v>
       </c>
       <c r="F3" t="n">
-        <v>6.269949629657978</v>
+        <v>1.018866814819422</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.40432630223781</v>
+        <v>5.103203024113645</v>
       </c>
       <c r="D4" t="n">
-        <v>31.51024035081684</v>
+        <v>5.120414057007736</v>
       </c>
       <c r="E4" t="n">
-        <v>6.451612669012473</v>
+        <v>1.048387058714527</v>
       </c>
       <c r="F4" t="n">
-        <v>6.269949629657978</v>
+        <v>1.018866814819422</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.51307698879548</v>
+        <v>2.845875010679265</v>
       </c>
       <c r="D5" t="n">
-        <v>17.54108862092325</v>
+        <v>2.850426900900028</v>
       </c>
       <c r="E5" t="n">
-        <v>6.451612669012473</v>
+        <v>1.048387058714527</v>
       </c>
       <c r="F5" t="n">
-        <v>6.269949629657978</v>
+        <v>1.018866814819422</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
